--- a/ig/DM-JUIN-2026/ValueSet-JDV-J227-NiveauExpertise-ROR.xlsx
+++ b/ig/DM-JUIN-2026/ValueSet-JDV-J227-NiveauExpertise-ROR.xlsx
@@ -9,13 +9,12 @@
     <sheet name="Metadata" r:id="rId3" sheetId="1"/>
     <sheet name="Include #0" r:id="rId4" sheetId="2"/>
     <sheet name="Include #1" r:id="rId5" sheetId="3"/>
-    <sheet name="Include #2" r:id="rId6" sheetId="4"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="139" uniqueCount="127">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="126">
   <si>
     <t>Property</t>
   </si>
@@ -368,34 +367,31 @@
     <t>Centre de ressources et de compétences sclérose en plaques (SEP)</t>
   </si>
   <si>
+    <t>49</t>
+  </si>
+  <si>
+    <t>Agrément Fédération Européenne des Services d'Urgence de la Main (FESUM) - SOS mains</t>
+  </si>
+  <si>
+    <t>50</t>
+  </si>
+  <si>
+    <t>Centre de Traitement des Brûlés (CTB)</t>
+  </si>
+  <si>
+    <t>51</t>
+  </si>
+  <si>
+    <t>Réseau France Santé</t>
+  </si>
+  <si>
+    <t>52</t>
+  </si>
+  <si>
+    <t>Autorisation par l’ARS pour la sous-traitance de préparation pharmaceutique</t>
+  </si>
+  <si>
     <t>https://mos.esante.gouv.fr/NOS/TRE_R344-NiveauExpertise/FHIR/TRE-R344-NiveauExpertise</t>
-  </si>
-  <si>
-    <t>0068</t>
-  </si>
-  <si>
-    <t>Chirurgie SOS main (Agrément FESUM Fédération européenne des services d'urgence de la main)</t>
-  </si>
-  <si>
-    <t>1641</t>
-  </si>
-  <si>
-    <t>Centre de Traitement des Brûlés (CTB)</t>
-  </si>
-  <si>
-    <t>1679</t>
-  </si>
-  <si>
-    <t>Réseau France Santé</t>
-  </si>
-  <si>
-    <t>1681</t>
-  </si>
-  <si>
-    <t>Autorisation par l’ARS pour la sous-traitance de préparation pharmaceutique</t>
-  </si>
-  <si>
-    <t>https://mos.esante.gouv.fr/NOS/TRE_R210-ActeSpecifique/FHIR/TRE-R210-ActeSpecifique</t>
   </si>
 </sst>
 </file>
@@ -727,7 +723,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B42"/>
+  <dimension ref="A1:B46"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="30.703125" customWidth="true"/>
@@ -1056,88 +1052,50 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>36</v>
+        <v>117</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>36</v>
+        <v>118</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
+        <v>119</v>
+      </c>
+      <c r="B42" t="s" s="2">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="s" s="2">
+        <v>121</v>
+      </c>
+      <c r="B43" t="s" s="2">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="s" s="2">
+        <v>123</v>
+      </c>
+      <c r="B44" t="s" s="2">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="B45" t="s" s="2">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="s" s="2">
         <v>37</v>
       </c>
-      <c r="B42" t="s" s="2">
-        <v>117</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B7"/>
-  <sheetFormatPr defaultRowHeight="15.0"/>
-  <cols>
-    <col min="1" max="1" width="30.703125" customWidth="true"/>
-    <col min="2" max="2" width="50.703125" customWidth="true"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="s" s="1">
-        <v>27</v>
-      </c>
-      <c r="B1" t="s" s="1">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="s" s="2">
-        <v>118</v>
-      </c>
-      <c r="B2" t="s" s="2">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="s" s="2">
-        <v>120</v>
-      </c>
-      <c r="B3" t="s" s="2">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="s" s="2">
-        <v>122</v>
-      </c>
-      <c r="B4" t="s" s="2">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="s" s="2">
-        <v>124</v>
-      </c>
-      <c r="B5" t="s" s="2">
+      <c r="B46" t="s" s="2">
         <v>125</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="s" s="2">
-        <v>36</v>
-      </c>
-      <c r="B6" t="s" s="2">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="B7" t="s" s="2">
-        <v>126</v>
       </c>
     </row>
   </sheetData>
